--- a/output/StructureDefinition-pdex-member-opt-out.xlsx
+++ b/output/StructureDefinition-pdex-member-opt-out.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$49</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1578" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1714" uniqueCount="347">
   <si>
     <t>Property</t>
   </si>
@@ -93,7 +93,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>A Group resource representing members who have opted out of data sharing. The Payer is the managing organization. The group members are the patients who have exercised their right to opt-out of sharing their health information, either broadly or for specific purposes or providers. This group is used to identify members whose data should not be shared in payer-to-payer or provider access scenarios.</t>
+    <t>A Group resource representing members who have opted out of Provider Access API data sharing. **Intended use:** this profile is offered as a payer-internal FHIR-based scaffolding pattern that implementers MAY adopt when their existing platform (legacy system, vendor product, internal API) cannot itself act as the authoritative reference source for opt-out determinations. Implementers whose existing systems can answer opt-out queries authoritatively are not required to use this profile. **Secondary use:** the same profile serves as the wire-format target profile for the `ConsentConstrainedMembers` output of the `$provider-member-match` operation; a ConsentConstrainedMembers Group returned by that operation conforms to this profile regardless of the mechanism the payer uses internally to determine opt-out status. **Privacy default — SHOULD suppress when opt-out status is sensitive.** Where a payer determines that disclosing opt-out status to a requesting provider would itself constitute a disclosure the member did not authorize (whether under applicable state privacy law, the member's stated preference, or the payer's privacy policy), the payer **SHOULD** suppress the `ConsentConstrainedMembers` output of `$provider-member-match` and instead include the affected members in the `NonMatchedMembers` Group; this makes the response indistinguishable to the requester between a true no-match and a matched-but-opted-out outcome. The internal-tracking use of this profile is unaffected by that choice. **Distinguishing master-list instances from operation-emitted response instances.** Both the payer-internal master opt-out list and the response Group emitted by `$provider-member-match` conform to this profile, so a payer storing both must distinguish them at query time. The recommended discriminator is `Group.identifier`: the payer SHOULD assign master-list instances a `Group.identifier` with a payer-defined `system` URI such as `https://{payer}/fhir/identifier/master-opt-out-list` (and a stable `value`), while operation-emitted response instances either omit `Group.identifier` or use a distinct system URI such as `https://{payer}/fhir/identifier/match-result`. Payers that prefer a tag-based discriminator MAY instead use `Group.meta.tag` with a payer-defined coding. `Group.code` is **not** a reliable discriminator here because it is fixed-pattern to `PdexMultiMemberMatchResultCS#consentconstraint` on every conformant instance (see FHIR-56493). The Payer is the managing organization, and Group.member entries reference the patients who have exercised their right to opt-out, either broadly or for specific purposes or providers.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -580,181 +580,10 @@
     <t>Kind of group (opt-out)</t>
   </si>
   <si>
-    <t>Classification for this opt-out group</t>
+    <t>Classification for this opt-out group. Fixed to `consentconstraint` because this profile represents only the consent-constrained / opt-out outcome from a multi-member match; the other codes in `PDexMultiMemberMatchResultVS` (`match`, `nomatch`) are not semantically applicable to instances of this profile.</t>
   </si>
   <si>
     <t>This would generally be omitted for Person resources.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/us/davinci-pdex/ValueSet/PDexMultiMemberMatchResultVS</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>FiveWs.what[x]</t>
-  </si>
-  <si>
-    <t>Group.name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Label for Group</t>
-  </si>
-  <si>
-    <t>A label assigned to the group for human identification and communication.</t>
-  </si>
-  <si>
-    <t>Used to identify the group in human communication.</t>
-  </si>
-  <si>
-    <t>./name[type="ST"]</t>
-  </si>
-  <si>
-    <t>Group.quantity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unsignedInt
-</t>
-  </si>
-  <si>
-    <t>Number of members who have opted out</t>
-  </si>
-  <si>
-    <t>The count of members in this opt-out group</t>
-  </si>
-  <si>
-    <t>Note that the quantity may be less than the number of members if some of the members are not active.</t>
-  </si>
-  <si>
-    <t>Group size is a common defining characteristic.</t>
-  </si>
-  <si>
-    <t>./quantity</t>
-  </si>
-  <si>
-    <t>Group.managingEntity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1|RelatedPerson|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>The Payer managing this opt-out group</t>
-  </si>
-  <si>
-    <t>Reference to the Payer organization that is managing and maintaining this opt-out group</t>
-  </si>
-  <si>
-    <t>This does not strictly align with ownership of a herd or flock, but may suffice to represent that relationship in simple cases. More complex cases will require an extension.</t>
-  </si>
-  <si>
-    <t>Group.characteristic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BackboneElement
-</t>
-  </si>
-  <si>
-    <t>Opt-out characteristics and scope</t>
-  </si>
-  <si>
-    <t>Characteristics describing the nature and scope of the opt-out</t>
-  </si>
-  <si>
-    <t>All the identified characteristics must be true for an entity to a member of the group.</t>
-  </si>
-  <si>
-    <t>Needs to be a generic mechanism for identifying what individuals can be part of a group.</t>
-  </si>
-  <si>
-    <t>./playedRole[isNormalRole()]/participation[isNormalParticipation() and typeCode="SBJ"]/act[isNormalAct and classCode="OBS" and moodCode="EVN"]</t>
-  </si>
-  <si>
-    <t>Group.characteristic.id</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Group.characteristic.extension</t>
-  </si>
-  <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>Group.characteristic.extension:optOutReason</t>
-  </si>
-  <si>
-    <t>optOutReason</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://hl7.org/fhir/us/davinci-pdex/StructureDefinition/opt-out-reason}
-</t>
-  </si>
-  <si>
-    <t>Reason for the opt-out</t>
-  </si>
-  <si>
-    <t>The member's stated reason for opting out</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>Group.characteristic.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user contentmodifiers</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>BackboneElement.modifierExtension</t>
-  </si>
-  <si>
-    <t>Group.characteristic.code</t>
-  </si>
-  <si>
-    <t>Identifies this as a consent constraint group</t>
-  </si>
-  <si>
-    <t>Fixed code indicating this group contains members with consent constraints (opt-outs)</t>
-  </si>
-  <si>
-    <t>Need a formal way of identifying the characteristic being described.</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -766,10 +595,239 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
+    <t>http://hl7.org/fhir/us/davinci-pdex/ValueSet/PDexMultiMemberMatchResultVS</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>FiveWs.what[x]</t>
+  </si>
+  <si>
+    <t>Group.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Label for Group</t>
+  </si>
+  <si>
+    <t>A label assigned to the group for human identification and communication.</t>
+  </si>
+  <si>
+    <t>Used to identify the group in human communication.</t>
+  </si>
+  <si>
+    <t>./name[type="ST"]</t>
+  </si>
+  <si>
+    <t>Group.quantity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unsignedInt
+</t>
+  </si>
+  <si>
+    <t>Number of members who have opted out</t>
+  </si>
+  <si>
+    <t>The count of members in this opt-out group</t>
+  </si>
+  <si>
+    <t>Note that the quantity may be less than the number of members if some of the members are not active.</t>
+  </si>
+  <si>
+    <t>Group size is a common defining characteristic.</t>
+  </si>
+  <si>
+    <t>./quantity</t>
+  </si>
+  <si>
+    <t>Group.managingEntity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Organization)
+</t>
+  </si>
+  <si>
+    <t>The Payer managing this opt-out group</t>
+  </si>
+  <si>
+    <t>Reference to the Payer organization that is managing and maintaining this opt-out group. Constrained to Organization since the managing entity is always a Payer (i.e., a healthcare organization), not a Practitioner, PractitionerRole, or RelatedPerson.</t>
+  </si>
+  <si>
+    <t>This does not strictly align with ownership of a herd or flock, but may suffice to represent that relationship in simple cases. More complex cases will require an extension.</t>
+  </si>
+  <si>
+    <t>Group.characteristic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BackboneElement
+</t>
+  </si>
+  <si>
+    <t>Opt-out characteristics and scope</t>
+  </si>
+  <si>
+    <t>Characteristics describing the nature and scope of the opt-out</t>
+  </si>
+  <si>
+    <t>All the identified characteristics must be true for an entity to a member of the group.</t>
+  </si>
+  <si>
+    <t>Needs to be a generic mechanism for identifying what individuals can be part of a group.</t>
+  </si>
+  <si>
+    <t>./playedRole[isNormalRole()]/participation[isNormalParticipation() and typeCode="SBJ"]/act[isNormalAct and classCode="OBS" and moodCode="EVN"]</t>
+  </si>
+  <si>
+    <t>Group.characteristic.id</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Group.characteristic.extension</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Group.characteristic.extension:optOutReason</t>
+  </si>
+  <si>
+    <t>optOutReason</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://hl7.org/fhir/us/davinci-pdex/StructureDefinition/opt-out-reason}
+</t>
+  </si>
+  <si>
+    <t>Reason for the opt-out</t>
+  </si>
+  <si>
+    <t>The member's stated reason for opting out</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>Group.characteristic.modifierExtension</t>
+  </si>
+  <si>
+    <t>extensions
+user contentmodifiers</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>BackboneElement.modifierExtension</t>
+  </si>
+  <si>
+    <t>Group.characteristic.code</t>
+  </si>
+  <si>
+    <t>Identifies this as a consent constraint group</t>
+  </si>
+  <si>
+    <t>Fixed code indicating this group contains members with consent constraints (opt-outs)</t>
+  </si>
+  <si>
+    <t>Need a formal way of identifying the characteristic being described.</t>
+  </si>
+  <si>
     <t>example</t>
   </si>
   <si>
     <t>List of characteristics used to describe group members; e.g. gender, age, owner, location, etc.</t>
+  </si>
+  <si>
+    <t>Group.characteristic.code.id</t>
+  </si>
+  <si>
+    <t>Group.characteristic.code.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Group.characteristic.code.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>Group.characteristic.code.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
     <t>Group.characteristic.value[x]</t>
@@ -828,12 +886,6 @@
   </si>
   <si>
     <t>Group.characteristic.period.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
   </si>
   <si>
     <t>Group.characteristic.period.start</t>
@@ -1386,7 +1438,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL45"/>
+  <dimension ref="A1:AL49"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="36.45703125" customWidth="true" bestFit="true"/>
@@ -1399,7 +1451,7 @@
     <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="71.28515625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="66.16015625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -3000,7 +3052,7 @@
         <v>78</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>78</v>
+        <v>183</v>
       </c>
       <c r="T15" t="s" s="2">
         <v>78</v>
@@ -3019,7 +3071,7 @@
       </c>
       <c r="Y15" s="2"/>
       <c r="Z15" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>78</v>
@@ -3052,18 +3104,18 @@
         <v>100</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3086,17 +3138,17 @@
         <v>89</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>78</v>
@@ -3145,7 +3197,7 @@
         <v>78</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -3160,7 +3212,7 @@
         <v>100</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>78</v>
@@ -3168,10 +3220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3194,19 +3246,19 @@
         <v>89</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>78</v>
@@ -3255,7 +3307,7 @@
         <v>78</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -3270,7 +3322,7 @@
         <v>100</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>78</v>
@@ -3278,10 +3330,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3304,16 +3356,16 @@
         <v>89</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3363,7 +3415,7 @@
         <v>78</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -3386,10 +3438,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3412,19 +3464,19 @@
         <v>78</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>78</v>
@@ -3473,7 +3525,7 @@
         <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -3488,7 +3540,7 @@
         <v>100</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>78</v>
@@ -3496,10 +3548,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3522,13 +3574,13 @@
         <v>78</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3579,7 +3631,7 @@
         <v>78</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -3594,7 +3646,7 @@
         <v>78</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>78</v>
@@ -3602,10 +3654,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3631,10 +3683,10 @@
         <v>134</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3673,17 +3725,17 @@
         <v>78</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AC21" s="2"/>
       <c r="AD21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -3706,13 +3758,13 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>78</v>
@@ -3734,13 +3786,13 @@
         <v>78</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3791,7 +3843,7 @@
         <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -3800,7 +3852,7 @@
         <v>80</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>139</v>
@@ -3814,14 +3866,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -3843,10 +3895,10 @@
         <v>134</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N23" t="s" s="2">
         <v>137</v>
@@ -3901,7 +3953,7 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -3924,10 +3976,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3953,14 +4005,14 @@
         <v>179</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>78</v>
@@ -3970,7 +4022,7 @@
         <v>78</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>237</v>
+        <v>183</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>78</v>
@@ -4009,7 +4061,7 @@
         <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>88</v>
@@ -4024,13 +4076,13 @@
         <v>100</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
         <v>240</v>
       </c>
@@ -4043,13 +4095,13 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>78</v>
@@ -4058,20 +4110,16 @@
         <v>78</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>241</v>
+        <v>213</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>244</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>78</v>
       </c>
@@ -4095,11 +4143,13 @@
         <v>78</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="Y25" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z25" t="s" s="2">
-        <v>245</v>
+        <v>78</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>78</v>
@@ -4117,10 +4167,10 @@
         <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>240</v>
+        <v>215</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>88</v>
@@ -4129,10 +4179,10 @@
         <v>78</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>246</v>
+        <v>216</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>78</v>
@@ -4140,21 +4190,21 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>78</v>
@@ -4166,20 +4216,18 @@
         <v>78</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>248</v>
+        <v>135</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>251</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>78</v>
       </c>
@@ -4188,7 +4236,7 @@
         <v>78</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>13</v>
+        <v>78</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>78</v>
@@ -4215,45 +4263,45 @@
         <v>78</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>78</v>
+        <v>220</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>78</v>
+        <v>243</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>78</v>
+        <v>221</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>247</v>
+        <v>222</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>252</v>
+        <v>216</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4264,28 +4312,32 @@
         <v>79</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J27" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="I27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J27" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="K27" t="s" s="2">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
+        <v>247</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="O27" t="s" s="2">
+        <v>249</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>78</v>
       </c>
@@ -4309,13 +4361,11 @@
         <v>78</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>78</v>
+        <v>184</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>78</v>
@@ -4333,13 +4383,13 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>78</v>
@@ -4348,7 +4398,7 @@
         <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>78</v>
+        <v>251</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>78</v>
@@ -4356,10 +4406,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4379,19 +4429,23 @@
         <v>78</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>212</v>
+        <v>253</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
+        <v>254</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>256</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>78</v>
       </c>
@@ -4439,7 +4493,7 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>214</v>
+        <v>257</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -4451,35 +4505,35 @@
         <v>78</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>215</v>
+        <v>258</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>78</v>
@@ -4488,18 +4542,20 @@
         <v>78</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>135</v>
+        <v>260</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O29" s="2"/>
+        <v>262</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>78</v>
       </c>
@@ -4523,57 +4579,55 @@
         <v>78</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="Y29" s="2"/>
       <c r="Z29" t="s" s="2">
-        <v>78</v>
+        <v>264</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>219</v>
+        <v>78</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>260</v>
+        <v>78</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>220</v>
+        <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>221</v>
+        <v>259</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>215</v>
+        <v>265</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4581,33 +4635,35 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>262</v>
+        <v>153</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="O30" s="2"/>
+        <v>269</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>270</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>78</v>
       </c>
@@ -4616,7 +4672,7 @@
         <v>78</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>78</v>
+        <v>13</v>
       </c>
       <c r="T30" t="s" s="2">
         <v>78</v>
@@ -4658,30 +4714,30 @@
         <v>266</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>88</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>267</v>
+        <v>78</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4695,33 +4751,29 @@
         <v>88</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>272</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q31" t="s" s="2">
-        <v>273</v>
-      </c>
+      <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
         <v>78</v>
       </c>
@@ -4765,7 +4817,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
@@ -4774,19 +4826,19 @@
         <v>88</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>267</v>
+        <v>78</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>275</v>
+        <v>78</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
         <v>276</v>
       </c>
@@ -4802,10 +4854,10 @@
         <v>79</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>78</v>
@@ -4814,18 +4866,16 @@
         <v>78</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>205</v>
+        <v>188</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>277</v>
+        <v>213</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>278</v>
+        <v>214</v>
       </c>
       <c r="N32" s="2"/>
-      <c r="O32" t="s" s="2">
-        <v>279</v>
-      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>78</v>
       </c>
@@ -4873,22 +4923,22 @@
         <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>276</v>
+        <v>215</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>176</v>
+        <v>78</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>280</v>
+        <v>216</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>78</v>
@@ -4896,21 +4946,21 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>78</v>
@@ -4922,15 +4972,17 @@
         <v>78</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>187</v>
+        <v>134</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>212</v>
+        <v>135</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>242</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>137</v>
+      </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>78</v>
@@ -4967,77 +5019,77 @@
         <v>78</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>78</v>
+        <v>220</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>78</v>
+        <v>243</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>78</v>
+        <v>221</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>78</v>
+        <v>139</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>134</v>
+        <v>279</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>135</v>
+        <v>280</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>259</v>
+        <v>281</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>137</v>
+        <v>282</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5087,22 +5139,22 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>221</v>
+        <v>283</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>78</v>
+        <v>284</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>215</v>
+        <v>285</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>78</v>
@@ -5110,50 +5162,50 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>229</v>
+        <v>78</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J35" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>134</v>
+        <v>279</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>230</v>
+        <v>287</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>231</v>
+        <v>288</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q35" s="2"/>
+      <c r="Q35" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="R35" t="s" s="2">
         <v>78</v>
       </c>
@@ -5197,22 +5249,22 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>232</v>
+        <v>291</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>78</v>
+        <v>284</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>131</v>
+        <v>292</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>78</v>
@@ -5220,10 +5272,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5231,10 +5283,10 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>89</v>
@@ -5246,16 +5298,18 @@
         <v>78</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>285</v>
+        <v>206</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
+      <c r="O36" t="s" s="2">
+        <v>296</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>78</v>
       </c>
@@ -5303,22 +5357,22 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>78</v>
+        <v>176</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>78</v>
+        <v>297</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>78</v>
@@ -5326,10 +5380,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5352,13 +5406,13 @@
         <v>78</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5409,7 +5463,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -5424,7 +5478,7 @@
         <v>78</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>78</v>
@@ -5432,10 +5486,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5464,7 +5518,7 @@
         <v>135</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>259</v>
+        <v>242</v>
       </c>
       <c r="N38" t="s" s="2">
         <v>137</v>
@@ -5505,19 +5559,19 @@
         <v>78</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>219</v>
+        <v>78</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>260</v>
+        <v>78</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>220</v>
+        <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -5532,7 +5586,7 @@
         <v>139</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>78</v>
@@ -5540,44 +5594,46 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="C39" t="s" s="2">
-        <v>291</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>78</v>
+        <v>230</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>292</v>
+        <v>134</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>293</v>
+        <v>231</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+        <v>232</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>78</v>
       </c>
@@ -5625,7 +5681,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -5640,18 +5696,18 @@
         <v>139</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>78</v>
+        <v>131</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5659,32 +5715,30 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>187</v>
+        <v>302</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>298</v>
-      </c>
+        <v>304</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>78</v>
@@ -5733,22 +5787,22 @@
         <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>88</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>300</v>
+        <v>78</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>131</v>
+        <v>78</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>78</v>
@@ -5756,10 +5810,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5779,20 +5833,18 @@
         <v>78</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>102</v>
+        <v>188</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>302</v>
+        <v>213</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>304</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>78</v>
@@ -5817,13 +5869,13 @@
         <v>78</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>305</v>
+        <v>78</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>306</v>
+        <v>78</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>307</v>
+        <v>78</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>78</v>
@@ -5841,7 +5893,7 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>308</v>
+        <v>215</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -5853,10 +5905,10 @@
         <v>78</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>131</v>
+        <v>216</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>78</v>
@@ -5864,21 +5916,21 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>78</v>
@@ -5887,19 +5939,19 @@
         <v>78</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>310</v>
+        <v>135</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>311</v>
+        <v>242</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>312</v>
+        <v>137</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -5937,34 +5989,34 @@
         <v>78</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>78</v>
+        <v>220</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>78</v>
+        <v>243</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>78</v>
+        <v>221</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>313</v>
+        <v>222</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>314</v>
+        <v>216</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>78</v>
@@ -5972,12 +6024,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="C43" s="2"/>
+        <v>306</v>
+      </c>
+      <c r="C43" t="s" s="2">
+        <v>308</v>
+      </c>
       <c r="D43" t="s" s="2">
         <v>78</v>
       </c>
@@ -5995,20 +6049,18 @@
         <v>78</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>187</v>
+        <v>309</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>318</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>78</v>
@@ -6057,22 +6109,22 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>319</v>
+        <v>222</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>131</v>
+        <v>78</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>78</v>
@@ -6080,10 +6132,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6103,27 +6155,25 @@
         <v>78</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>254</v>
+        <v>188</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" t="s" s="2">
-        <v>323</v>
-      </c>
+        <v>314</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q44" t="s" s="2">
-        <v>324</v>
-      </c>
+      <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
         <v>78</v>
       </c>
@@ -6167,7 +6217,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -6176,13 +6226,13 @@
         <v>88</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>78</v>
+        <v>317</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>78</v>
+        <v>131</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>78</v>
@@ -6190,10 +6240,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6213,27 +6263,25 @@
         <v>78</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>153</v>
+        <v>102</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" t="s" s="2">
-        <v>328</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q45" t="s" s="2">
-        <v>329</v>
-      </c>
+      <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
         <v>78</v>
       </c>
@@ -6253,13 +6301,13 @@
         <v>78</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>78</v>
+        <v>322</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>78</v>
+        <v>323</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>78</v>
+        <v>324</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>78</v>
@@ -6292,14 +6340,450 @@
         <v>100</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>78</v>
+        <v>131</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>78</v>
       </c>
     </row>
+    <row r="46" hidden="true">
+      <c r="A46" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="F46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="O46" s="2"/>
+      <c r="P46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q46" s="2"/>
+      <c r="R46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="47" hidden="true">
+      <c r="A47" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K47" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="O47" s="2"/>
+      <c r="P47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q47" s="2"/>
+      <c r="R47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="48" hidden="true">
+      <c r="A48" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="F48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K48" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="P48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q48" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="R48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="49" hidden="true">
+      <c r="A49" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="D49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K49" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="P49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q49" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="R49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>342</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AL45">
+  <autoFilter ref="A1:AL49">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -6309,7 +6793,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI44">
+  <conditionalFormatting sqref="A2:AI48">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
